--- a/output/graficos_dimensiones/comunal_i_ingr_a_2022_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2022_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:10</t>
+    <t xml:space="preserve">2026-09-09 23:04</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2022_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2022_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:04</t>
+    <t xml:space="preserve">2026-09-17 14:01</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2022_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2022_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 14:01</t>
+    <t xml:space="preserve">2026-09-23 12:30</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2022_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2022_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:30</t>
+    <t xml:space="preserve">2026-10-02 14:13</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2022_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2022_biobio.xlsx
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Hualpén</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Angeles</t>
+    <t xml:space="preserve">Los Ángeles</t>
   </si>
   <si>
     <t xml:space="preserve">Coronel</t>
@@ -123,7 +123,7 @@
     <t xml:space="preserve">Contulmo</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Alamos</t>
+    <t xml:space="preserve">Los Álamos</t>
   </si>
   <si>
     <t xml:space="preserve">Lebu</t>
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 14:13</t>
+    <t xml:space="preserve">2026-10-04 08:52</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2022_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2022_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 08:52</t>
+    <t xml:space="preserve">2026-10-05 10:15</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -1056,7 +1056,7 @@
         <v>2022</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>777176.62</v>
+        <v>777176.63</v>
       </c>
     </row>
     <row r="31">
